--- a/output/2026-09-03_20_Italia_Basilicata_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-03_20_Italia_Basilicata_Utensilerie_e_Macchine_Utensili.xlsx
@@ -498,7 +498,6 @@
           <t>+39 0971 472210</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Azienda storica (attiva dal 1975/1995), sede in Via della Fisica 26, Zona Industriale, Potenza. Verificata su sito ufficiale, europages.it, kompass.it, amministrazionicomunali.it.</t>
@@ -536,7 +535,6 @@
           <t>0971 58417 / 0971 57769</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Storica ferramenta (dal 1935), sede in Complanare Varco d'Izzo 14, Potenza. Verificata su sito ufficiale, paginebianche.it, firmania.it.</t>
@@ -574,7 +572,6 @@
           <t>0971 651122 / 0971 651540</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Via Enrico De Nicola 19, Tito (PZ). Specializzata in attrezzature per autofficine/gommisti; classificazione ufficiale ATECO risulta commercio ingrosso macchine utensili. Email 'info@faref.org' fornita in origine non confermata da fonti indipendenti (dominio storico non più in uso), lasciata vuota.</t>
@@ -592,7 +589,6 @@
           <t>Signore S.n.c.</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Potenza</t>
@@ -608,7 +604,6 @@
           <t>0972 88537</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Via S. Francesco 113, Lavello (PZ). Entità distinta da Metalsica Snc (stessa famiglia Signore ma sede e telefono differenti); il sito signoreshop.com risulta associato a Metalsica, non a questa sede, per questo lasciato vuoto.</t>
@@ -668,7 +663,6 @@
           <t>Top Utensili S.r.l.</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Matera</t>
@@ -684,7 +678,6 @@
           <t>0835 388970 / 0835 309141</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Via dei Mestieri 1 (anche riportato 45/C-D), Matera. Classificata su directory (misterimprese.it) come 'Macchine utensili - commercio'.</t>
@@ -729,7 +722,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sede operativa Via del Commercio, Zona PAIP 2, Matera. Email confermata via directory (paginebianche.it).</t>
+          <t>Sede operativa Via del Commercio, Zona PAIP 2, Matera. Email confermata via directory (paginebianche.it). [DUPLICATO — vedi anche: 2026-09-03_19_Italia_Basilicata_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -744,7 +737,6 @@
           <t>Decorsud di Berardino Lapenna &amp; C. S.n.c.</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Matera</t>
@@ -760,7 +752,6 @@
           <t>0835 549924</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Contrada Cupa, Bernalda (MT). Attività ufficialmente registrata come commercio ingrosso ferramenta (ATECO 5115).</t>
@@ -778,7 +769,6 @@
           <t>Ferramenta Natrella (Natrella Antonio)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>Matera</t>

--- a/output/2026-09-03_20_Italia_Basilicata_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-03_20_Italia_Basilicata_Utensilerie_e_Macchine_Utensili.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -542,7 +542,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
